--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -125,52 +125,46 @@
     <t>QQ皮肤</t>
   </si>
   <si>
-    <t>laowanjia</t>
-  </si>
-  <si>
-    <t>老玩家皮肤</t>
+    <t>wujin666</t>
+  </si>
+  <si>
+    <t>无尽皮肤</t>
   </si>
   <si>
     <t>hp666</t>
   </si>
   <si>
+    <t>5001</t>
+  </si>
+  <si>
+    <t>6666</t>
+  </si>
+  <si>
+    <t>pl礼包</t>
+  </si>
+  <si>
+    <t>qq1000</t>
+  </si>
+  <si>
+    <t>入群礼包</t>
+  </si>
+  <si>
+    <t>qq2000</t>
+  </si>
+  <si>
+    <t>qq3000</t>
+  </si>
+  <si>
+    <t>之后的及时删除</t>
+  </si>
+  <si>
+    <t>gx426</t>
+  </si>
+  <si>
     <t>9,5,9</t>
   </si>
   <si>
     <t>4003,4004,4013</t>
-  </si>
-  <si>
-    <t>6666,666,666</t>
-  </si>
-  <si>
-    <t>pl礼包</t>
-  </si>
-  <si>
-    <t>qq1000</t>
-  </si>
-  <si>
-    <t>1888,188,188</t>
-  </si>
-  <si>
-    <t>入群礼包</t>
-  </si>
-  <si>
-    <t>qq2000</t>
-  </si>
-  <si>
-    <t>2888,288,288</t>
-  </si>
-  <si>
-    <t>qq3000</t>
-  </si>
-  <si>
-    <t>3888,388,388</t>
-  </si>
-  <si>
-    <t>之后的及时删除</t>
-  </si>
-  <si>
-    <t>gx426</t>
   </si>
   <si>
     <t>1000,100,100</t>
@@ -593,12 +587,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1559,6 +1553,12 @@
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1569,19 +1569,25 @@
         <v>21</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1589,22 +1595,28 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1612,19 +1624,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>30</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:9">
@@ -1641,19 +1653,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" s="5" customFormat="1" customHeight="1" spans="1:9">
@@ -1661,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -1672,16 +1684,16 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:9">
@@ -1692,16 +1704,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:9">
@@ -1718,16 +1730,16 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:9">
@@ -1758,19 +1770,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:9">
@@ -2004,19 +2016,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="I6" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2027,19 +2039,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="I7" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2050,19 +2062,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="I8" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2073,19 +2085,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2096,19 +2108,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="I10" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2119,19 +2131,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="I11" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2160,19 +2172,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="H16" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="I16" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="J16" s="1"/>
     </row>
@@ -2186,19 +2198,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="H17" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="I17" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="J17" s="1"/>
     </row>
@@ -2212,19 +2224,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="H18" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="I18" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="J18" s="1"/>
     </row>
@@ -2238,19 +2250,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="H19" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="I19" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="J19" s="1"/>
     </row>
@@ -2264,25 +2276,25 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="I20" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" customHeight="1" spans="1:10">
       <c r="G21" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H21" s="4"/>
     </row>
@@ -2414,7 +2426,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -2426,7 +2438,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2437,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F7" s="1">
         <v>4</v>
@@ -2449,7 +2461,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2460,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F8" s="1">
         <v>4</v>
@@ -2472,7 +2484,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2483,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
@@ -2495,7 +2507,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2506,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F10" s="1">
         <v>4</v>
@@ -2518,7 +2530,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2529,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F11" s="1">
         <v>4</v>
@@ -2541,7 +2553,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2552,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F12" s="1">
         <v>4</v>
@@ -2564,7 +2576,7 @@
         <v>7</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2575,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F13" s="1">
         <v>4</v>
@@ -2587,7 +2599,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2598,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F14" s="1">
         <v>4</v>
@@ -2610,7 +2622,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2621,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -2633,7 +2645,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2644,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F17" s="1">
         <v>4</v>
@@ -2656,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2667,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F18" s="1">
         <v>4</v>
@@ -2679,7 +2691,7 @@
         <v>2</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2690,7 +2702,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F19" s="1">
         <v>4</v>
@@ -2702,7 +2714,7 @@
         <v>3</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2713,7 +2725,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F20" s="1">
         <v>4</v>
@@ -2725,7 +2737,7 @@
         <v>4</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2736,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F21" s="1">
         <v>4</v>
@@ -2748,7 +2760,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2759,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F22" s="1">
         <v>4</v>
@@ -2771,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2782,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F23" s="1">
         <v>4</v>
@@ -2794,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2805,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F24" s="1">
         <v>4</v>
@@ -2817,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2828,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F25" s="1">
         <v>4</v>
@@ -2840,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2851,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F26" s="1">
         <v>4</v>
@@ -2863,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="3:9">
@@ -2883,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F29" s="1">
         <v>4</v>
@@ -2895,7 +2907,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2906,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F30" s="1">
         <v>4</v>
@@ -2918,7 +2930,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2929,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F31" s="1">
         <v>4</v>
@@ -2941,7 +2953,7 @@
         <v>3</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2952,7 +2964,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F32" s="1">
         <v>4</v>
@@ -2964,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2975,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F33" s="1">
         <v>4</v>
@@ -2987,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2998,7 +3010,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F34" s="1">
         <v>4</v>
@@ -3010,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" customFormat="1" customHeight="1" spans="1:10">
@@ -3169,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -3181,7 +3193,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3228,7 +3240,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -53,11 +58,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-9 副本劵
-5 boss劵和其他材料
-1 金币，亿单位
-7 礼包
-3 技能书</t>
+0 金币，百万单位
+</t>
         </r>
       </text>
     </comment>
@@ -66,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="112">
   <si>
     <t>#</t>
   </si>
@@ -134,18 +136,27 @@
     <t>hp666</t>
   </si>
   <si>
+    <t>0,5,5</t>
+  </si>
+  <si>
+    <t>0,5001,5002</t>
+  </si>
+  <si>
+    <t>8,8888,88</t>
+  </si>
+  <si>
+    <t>pl礼包</t>
+  </si>
+  <si>
+    <t>qq1000</t>
+  </si>
+  <si>
     <t>5001</t>
   </si>
   <si>
     <t>6666</t>
   </si>
   <si>
-    <t>pl礼包</t>
-  </si>
-  <si>
-    <t>qq1000</t>
-  </si>
-  <si>
     <t>入群礼包</t>
   </si>
   <si>
@@ -158,31 +169,34 @@
     <t>之后的及时删除</t>
   </si>
   <si>
-    <t>gx426</t>
+    <t>gx100</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>0,5001</t>
+  </si>
+  <si>
+    <t>5,5000</t>
+  </si>
+  <si>
+    <t>zhanchong100</t>
+  </si>
+  <si>
+    <t>0,5002</t>
+  </si>
+  <si>
+    <t>4,100</t>
+  </si>
+  <si>
+    <t>anyult18ccc</t>
   </si>
   <si>
     <t>9,5,9</t>
   </si>
   <si>
     <t>4003,4004,4013</t>
-  </si>
-  <si>
-    <t>1000,100,100</t>
-  </si>
-  <si>
-    <t>anyu426</t>
-  </si>
-  <si>
-    <t>20000,2000,1600</t>
-  </si>
-  <si>
-    <t>yuandan2026</t>
-  </si>
-  <si>
-    <t>2000,200,200</t>
-  </si>
-  <si>
-    <t>anyult18ccc</t>
   </si>
   <si>
     <t>3888,688,688</t>
@@ -587,12 +601,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1392,7 +1406,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1553,12 +1567,6 @@
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1569,16 +1577,16 @@
         <v>21</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:9">
@@ -1595,19 +1603,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:9">
@@ -1624,19 +1632,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:9">
@@ -1653,19 +1661,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" s="5" customFormat="1" customHeight="1" spans="1:9">
@@ -1673,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:9">
@@ -1684,16 +1692,16 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:9">
@@ -1704,43 +1712,20 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>31</v>
-      </c>
       <c r="G16" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:9">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="1">
-        <v>43</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" customHeight="1" spans="1:9">
       <c r="H18" s="4"/>
@@ -1749,44 +1734,44 @@
       <c r="H19" s="4"/>
     </row>
     <row r="20" customHeight="1" spans="1:9">
+      <c r="E20" s="6"/>
       <c r="H20" s="4"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" customHeight="1" spans="1:9">
-      <c r="E21" s="6"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="6"/>
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>113</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="22" customHeight="1" spans="1:9">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1">
-        <v>113</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:9">
-      <c r="H23" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:9">
+      <c r="H25" s="4"/>
     </row>
     <row r="26" customHeight="1" spans="1:9">
       <c r="H26" s="4"/>
@@ -1797,8 +1782,8 @@
     <row r="28" customHeight="1" spans="1:9">
       <c r="H28" s="4"/>
     </row>
-    <row r="29" customHeight="1" spans="1:9">
-      <c r="H29" s="4"/>
+    <row r="30" customHeight="1" spans="1:9">
+      <c r="H30" s="4"/>
     </row>
     <row r="31" customHeight="1" spans="1:9">
       <c r="H31" s="4"/>
@@ -1808,16 +1793,16 @@
     </row>
     <row r="33" customHeight="1" spans="8:11">
       <c r="H33" s="4"/>
+      <c r="K33" s="7"/>
     </row>
     <row r="34" customHeight="1" spans="8:11">
       <c r="H34" s="4"/>
-      <c r="K34" s="7"/>
     </row>
     <row r="35" customHeight="1" spans="8:11">
       <c r="H35" s="4"/>
     </row>
-    <row r="36" customHeight="1" spans="8:11">
-      <c r="H36" s="4"/>
+    <row r="38" customHeight="1" spans="8:11">
+      <c r="H38" s="4"/>
     </row>
     <row r="39" customHeight="1" spans="8:11">
       <c r="H39" s="4"/>
@@ -1825,8 +1810,8 @@
     <row r="40" customHeight="1" spans="8:11">
       <c r="H40" s="4"/>
     </row>
-    <row r="41" customHeight="1" spans="8:11">
-      <c r="H41" s="4"/>
+    <row r="42" customHeight="1" spans="8:11">
+      <c r="H42" s="4"/>
     </row>
     <row r="43" customHeight="1" spans="8:11">
       <c r="H43" s="4"/>
@@ -1837,8 +1822,8 @@
     <row r="45" customHeight="1" spans="8:11">
       <c r="H45" s="4"/>
     </row>
-    <row r="46" customHeight="1" spans="8:11">
-      <c r="H46" s="4"/>
+    <row r="47" customHeight="1" spans="8:11">
+      <c r="H47" s="4"/>
     </row>
     <row r="48" customHeight="1" spans="8:11">
       <c r="H48" s="4"/>
@@ -1846,8 +1831,8 @@
     <row r="49" customHeight="1" spans="8:8">
       <c r="H49" s="4"/>
     </row>
-    <row r="50" customHeight="1" spans="8:8">
-      <c r="H50" s="4"/>
+    <row r="51" customHeight="1" spans="8:8">
+      <c r="H51" s="4"/>
     </row>
     <row r="52" customHeight="1" spans="8:8">
       <c r="H52" s="4"/>
@@ -1861,14 +1846,11 @@
     <row r="55" customHeight="1" spans="8:8">
       <c r="H55" s="4"/>
     </row>
-    <row r="56" customHeight="1" spans="8:8">
-      <c r="H56" s="4"/>
-    </row>
-    <row r="58" customHeight="1" spans="8:8">
-      <c r="H58" s="4"/>
-    </row>
-    <row r="60" customHeight="1" spans="8:8">
-      <c r="H60" s="4"/>
+    <row r="57" customHeight="1" spans="8:8">
+      <c r="H57" s="4"/>
+    </row>
+    <row r="59" customHeight="1" spans="8:8">
+      <c r="H59" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2016,19 +1998,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2039,19 +2021,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="G7" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2062,19 +2044,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="H8" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2085,19 +2067,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2108,19 +2090,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2131,19 +2113,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2172,19 +2154,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J16" s="1"/>
     </row>
@@ -2198,19 +2180,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J17" s="1"/>
     </row>
@@ -2224,19 +2206,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J18" s="1"/>
     </row>
@@ -2250,19 +2232,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J19" s="1"/>
     </row>
@@ -2276,25 +2258,25 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="G20" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" customHeight="1" spans="1:10">
       <c r="G21" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H21" s="4"/>
     </row>
@@ -2426,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -2438,7 +2420,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2449,7 +2431,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F7" s="1">
         <v>4</v>
@@ -2461,7 +2443,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2472,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F8" s="1">
         <v>4</v>
@@ -2484,7 +2466,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2495,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
@@ -2507,7 +2489,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2518,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F10" s="1">
         <v>4</v>
@@ -2530,7 +2512,7 @@
         <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2541,7 +2523,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F11" s="1">
         <v>4</v>
@@ -2553,7 +2535,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2564,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F12" s="1">
         <v>4</v>
@@ -2576,7 +2558,7 @@
         <v>7</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2587,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F13" s="1">
         <v>4</v>
@@ -2599,7 +2581,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2610,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F14" s="1">
         <v>4</v>
@@ -2622,7 +2604,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2633,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -2645,7 +2627,7 @@
         <v>10</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2656,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F17" s="1">
         <v>4</v>
@@ -2668,7 +2650,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2679,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F18" s="1">
         <v>4</v>
@@ -2691,7 +2673,7 @@
         <v>2</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2702,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F19" s="1">
         <v>4</v>
@@ -2714,7 +2696,7 @@
         <v>3</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2725,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F20" s="1">
         <v>4</v>
@@ -2737,7 +2719,7 @@
         <v>4</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2748,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F21" s="1">
         <v>4</v>
@@ -2760,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2771,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F22" s="1">
         <v>4</v>
@@ -2783,7 +2765,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2794,7 +2776,7 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F23" s="1">
         <v>4</v>
@@ -2806,7 +2788,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2817,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F24" s="1">
         <v>4</v>
@@ -2829,7 +2811,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2840,7 +2822,7 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F25" s="1">
         <v>4</v>
@@ -2852,7 +2834,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2863,7 +2845,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F26" s="1">
         <v>4</v>
@@ -2875,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="3:9">
@@ -2895,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F29" s="1">
         <v>4</v>
@@ -2907,7 +2889,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2918,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F30" s="1">
         <v>4</v>
@@ -2930,7 +2912,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2941,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F31" s="1">
         <v>4</v>
@@ -2953,7 +2935,7 @@
         <v>3</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2964,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F32" s="1">
         <v>4</v>
@@ -2976,7 +2958,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2987,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F33" s="1">
         <v>4</v>
@@ -2999,7 +2981,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -3010,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F34" s="1">
         <v>4</v>
@@ -3022,7 +3004,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" customFormat="1" customHeight="1" spans="1:10">
@@ -3181,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -3193,7 +3175,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3240,7 +3222,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="112">
   <si>
     <t>#</t>
   </si>
@@ -148,22 +148,22 @@
     <t>pl礼包</t>
   </si>
   <si>
+    <t>qq500</t>
+  </si>
+  <si>
+    <t>5,5555,55</t>
+  </si>
+  <si>
+    <t>入群礼包</t>
+  </si>
+  <si>
     <t>qq1000</t>
   </si>
   <si>
-    <t>5001</t>
-  </si>
-  <si>
-    <t>6666</t>
-  </si>
-  <si>
-    <t>入群礼包</t>
-  </si>
-  <si>
-    <t>qq2000</t>
-  </si>
-  <si>
-    <t>qq3000</t>
+    <t>6,6666,66</t>
+  </si>
+  <si>
+    <t>qq1500</t>
   </si>
   <si>
     <t>之后的及时删除</t>
@@ -1590,12 +1590,6 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1606,25 +1600,19 @@
         <v>26</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1632,28 +1620,22 @@
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1664,16 +1646,16 @@
         <v>31</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" s="5" customFormat="1" customHeight="1" spans="1:9">

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -14,8 +14,7 @@
   <sheets>
     <sheet name="更新码" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="6" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="9" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="9" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="57">
   <si>
     <t>#</t>
   </si>
@@ -166,6 +165,15 @@
     <t>qq1500</t>
   </si>
   <si>
+    <t>pf001</t>
+  </si>
+  <si>
+    <t>pf礼包</t>
+  </si>
+  <si>
+    <t>pf002</t>
+  </si>
+  <si>
     <t>之后的及时删除</t>
   </si>
   <si>
@@ -181,28 +189,13 @@
     <t>5,5000</t>
   </si>
   <si>
-    <t>zhanchong100</t>
+    <t>zc100</t>
   </si>
   <si>
     <t>0,5002</t>
   </si>
   <si>
-    <t>4,100</t>
-  </si>
-  <si>
-    <t>anyult18ccc</t>
-  </si>
-  <si>
-    <t>9,5,9</t>
-  </si>
-  <si>
-    <t>4003,4004,4013</t>
-  </si>
-  <si>
-    <t>3888,688,688</t>
-  </si>
-  <si>
-    <t>副本券2888，Boss券388，传世券288</t>
+    <t>5,100</t>
   </si>
   <si>
     <t>dki309d!34</t>
@@ -238,166 +231,7 @@
     <t>io&amp;zsd136</t>
   </si>
   <si>
-    <t>xinshou1</t>
-  </si>
-  <si>
-    <t>4,4,4,4,5,9,4,5,5</t>
-  </si>
-  <si>
-    <t>9,27,22,98,4008,4003,106,4001,4007</t>
-  </si>
-  <si>
-    <t>1,1,2,1,1580,20000,1,50000000,500000</t>
-  </si>
-  <si>
-    <t>9、10阶技能自选各一个+特戒自选*1+1套专属+30级翅膀（1580个羽毛）+5000副本卷</t>
-  </si>
-  <si>
-    <t>xinshou2</t>
-  </si>
-  <si>
-    <t>4,4,4,4,5,9,4,4,4,5,5</t>
-  </si>
-  <si>
-    <t>9,27,22,98,4008,4003,26,29,106,4001,4007</t>
-  </si>
-  <si>
-    <t>1,1,4,2,2205,40000,5,1,2,100000000,1200000</t>
-  </si>
-  <si>
-    <t>9、10、11阶级技能各一个+特戒自选*2+2套专属+35级翅膀（2205个羽毛）+10000副本卷+5神技</t>
-  </si>
-  <si>
-    <t>xinshou3</t>
-  </si>
-  <si>
-    <t>4,4,4,4,5,5,9,4,4,4,4,5,5,5</t>
-  </si>
-  <si>
-    <t>9,27,22,98,4008,4004,4003,26,29,106,107,4001,4006,4007</t>
-  </si>
-  <si>
-    <t>1,1,6,3,2955,5000,80000,10,1,5,1,200000000,100000,3000000</t>
-  </si>
-  <si>
-    <t>9、10、11阶技能自选各一个+特戒自选*3+35级翅膀+3套专属自选套*1+20000副本卷+2000boos卷+10神技</t>
-  </si>
-  <si>
-    <t>xinshou4</t>
-  </si>
-  <si>
-    <t>4,4,4,4,18,18,5,5,9,9,4,4,4,4,4,5,5,5,4,5,5</t>
-  </si>
-  <si>
-    <t>9,27,22,98,180030,180001,4008,4004,4003,4013,26,29,106,107,108,4001,4006,4102,204,4022,4007</t>
-  </si>
-  <si>
-    <t>1,2,10,4,10,1,4830,8000,120000,5000,20,1,10,2,1,1000000000,200000,1000,2,200000,40000000</t>
-  </si>
-  <si>
-    <t>9、10、11阶技能自选各一个+特戒自选*4+4套专属自选+50级翅膀(4830个羽毛)+极黑奴*10+20神技+30000副本卷+3000boos卷+1000传世卷</t>
-  </si>
-  <si>
-    <t>xinshou5</t>
-  </si>
-  <si>
-    <t>9,27,22,98,180030,180001,4008,4004,4003,4013,26,29,106,107,108,4001,4006,4102,207,4022,4007</t>
-  </si>
-  <si>
-    <t>1,3,20,6,20,2,7205,15000,200000,10000,40,1,20,4,2,2000000000,400000,2000,2,500000,80000000</t>
-  </si>
-  <si>
-    <t>9、10、11阶技能自选各一个+特戒自选*6+6套专属自选+60级羽毛（7205个羽毛）+极黑奴*20+40神技+50000副本卷+4000boos卷+2000传世卷</t>
-  </si>
-  <si>
     <t>.</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd001</t>
-  </si>
-  <si>
-    <t>白银礼包</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd002</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd003</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd004</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd005</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd006</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd007</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd008</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd009</t>
-  </si>
-  <si>
-    <t>*Zr3dkYpd010</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd001</t>
-  </si>
-  <si>
-    <t>黄金礼包</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd002</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd003</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd004</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd005</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd006</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd007</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd008</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd009</t>
-  </si>
-  <si>
-    <t>Nd(3dkepd010</t>
-  </si>
-  <si>
-    <t>Ud^3dkepd001</t>
-  </si>
-  <si>
-    <t>钻石礼包</t>
-  </si>
-  <si>
-    <t>Ud^3dkepd002</t>
-  </si>
-  <si>
-    <t>Ud^3dkepd003</t>
-  </si>
-  <si>
-    <t>Ud^3dkepd004</t>
-  </si>
-  <si>
-    <t>Ud^3dkepd005</t>
-  </si>
-  <si>
-    <t>Ud^3dkepd006</t>
   </si>
   <si>
     <t>dalao</t>
@@ -1406,7 +1240,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1658,124 +1492,143 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A14" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="5" t="s">
+    <row r="14" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
+      <c r="F14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
       <c r="C15" s="1">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" s="8" t="s">
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A18" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="9" t="s">
+    </row>
+    <row r="19" customHeight="1" spans="1:9">
+      <c r="C19" s="1">
+        <v>41</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:9">
-      <c r="C16" s="1">
+      <c r="F19" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:9">
+      <c r="C20" s="1">
         <v>42</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D20" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:9">
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:9">
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
-      <c r="E20" s="6"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="6"/>
+      <c r="G20" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1">
-        <v>113</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="H22" s="4"/>
     </row>
+    <row r="23" customHeight="1" spans="1:9">
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:9">
+      <c r="E24" s="6"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="6"/>
+    </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="H25" s="4"/>
     </row>
-    <row r="26" customHeight="1" spans="1:9">
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" customHeight="1" spans="1:9">
-      <c r="H27" s="4"/>
-    </row>
     <row r="28" customHeight="1" spans="1:9">
       <c r="H28" s="4"/>
     </row>
+    <row r="29" customHeight="1" spans="1:9">
+      <c r="H29" s="4"/>
+    </row>
     <row r="30" customHeight="1" spans="1:9">
       <c r="H30" s="4"/>
     </row>
     <row r="31" customHeight="1" spans="1:9">
       <c r="H31" s="4"/>
     </row>
-    <row r="32" customHeight="1" spans="1:9">
-      <c r="H32" s="4"/>
-    </row>
     <row r="33" customHeight="1" spans="8:11">
       <c r="H33" s="4"/>
-      <c r="K33" s="7"/>
     </row>
     <row r="34" customHeight="1" spans="8:11">
       <c r="H34" s="4"/>
@@ -1783,14 +1636,18 @@
     <row r="35" customHeight="1" spans="8:11">
       <c r="H35" s="4"/>
     </row>
+    <row r="36" customHeight="1" spans="8:11">
+      <c r="H36" s="4"/>
+      <c r="K36" s="7"/>
+    </row>
+    <row r="37" customHeight="1" spans="8:11">
+      <c r="H37" s="4"/>
+    </row>
     <row r="38" customHeight="1" spans="8:11">
       <c r="H38" s="4"/>
     </row>
-    <row r="39" customHeight="1" spans="8:11">
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" customHeight="1" spans="8:11">
-      <c r="H40" s="4"/>
+    <row r="41" customHeight="1" spans="8:11">
+      <c r="H41" s="4"/>
     </row>
     <row r="42" customHeight="1" spans="8:11">
       <c r="H42" s="4"/>
@@ -1798,20 +1655,20 @@
     <row r="43" customHeight="1" spans="8:11">
       <c r="H43" s="4"/>
     </row>
-    <row r="44" customHeight="1" spans="8:11">
-      <c r="H44" s="4"/>
-    </row>
     <row r="45" customHeight="1" spans="8:11">
       <c r="H45" s="4"/>
     </row>
+    <row r="46" customHeight="1" spans="8:11">
+      <c r="H46" s="4"/>
+    </row>
     <row r="47" customHeight="1" spans="8:11">
       <c r="H47" s="4"/>
     </row>
     <row r="48" customHeight="1" spans="8:11">
       <c r="H48" s="4"/>
     </row>
-    <row r="49" customHeight="1" spans="8:8">
-      <c r="H49" s="4"/>
+    <row r="50" customHeight="1" spans="8:8">
+      <c r="H50" s="4"/>
     </row>
     <row r="51" customHeight="1" spans="8:8">
       <c r="H51" s="4"/>
@@ -1819,20 +1676,26 @@
     <row r="52" customHeight="1" spans="8:8">
       <c r="H52" s="4"/>
     </row>
-    <row r="53" customHeight="1" spans="8:8">
-      <c r="H53" s="4"/>
-    </row>
     <row r="54" customHeight="1" spans="8:8">
       <c r="H54" s="4"/>
     </row>
     <row r="55" customHeight="1" spans="8:8">
       <c r="H55" s="4"/>
     </row>
+    <row r="56" customHeight="1" spans="8:8">
+      <c r="H56" s="4"/>
+    </row>
     <row r="57" customHeight="1" spans="8:8">
       <c r="H57" s="4"/>
     </row>
-    <row r="59" customHeight="1" spans="8:8">
-      <c r="H59" s="4"/>
+    <row r="58" customHeight="1" spans="8:8">
+      <c r="H58" s="4"/>
+    </row>
+    <row r="60" customHeight="1" spans="8:8">
+      <c r="H60" s="4"/>
+    </row>
+    <row r="62" customHeight="1" spans="8:8">
+      <c r="H62" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1850,7 +1713,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1980,19 +1843,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="I6" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2003,19 +1866,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="I7" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2026,19 +1889,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="I8" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2049,19 +1912,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2072,19 +1935,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="I10" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2095,19 +1958,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="I11" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2126,144 +1989,14 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" customFormat="1" customHeight="1" spans="1:19">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1">
-        <v>19001</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1">
-        <v>19002</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1">
-        <v>19003</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1">
-        <v>19004</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" s="1"/>
-    </row>
-    <row r="20" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1">
-        <v>19005</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:10">
-      <c r="G21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:10">
-      <c r="H22" s="4"/>
+    <row r="16" customHeight="1" spans="1:19">
+      <c r="G16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" customHeight="1" spans="8:8">
+      <c r="H17" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2279,749 +2012,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
-  <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="22.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="24.125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="I2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C6" s="1">
-        <v>23001</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F6" s="1">
-        <v>4</v>
-      </c>
-      <c r="G6" s="1">
-        <v>106</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C7" s="1">
-        <v>23002</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="1">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1">
-        <v>106</v>
-      </c>
-      <c r="H7" s="1">
-        <v>2</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C8" s="1">
-        <v>23003</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F8" s="1">
-        <v>4</v>
-      </c>
-      <c r="G8" s="1">
-        <v>106</v>
-      </c>
-      <c r="H8" s="1">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C9" s="1">
-        <v>23004</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" s="1">
-        <v>4</v>
-      </c>
-      <c r="G9" s="1">
-        <v>106</v>
-      </c>
-      <c r="H9" s="1">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C10" s="1">
-        <v>23005</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="1">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1">
-        <v>106</v>
-      </c>
-      <c r="H10" s="1">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C11" s="1">
-        <v>23006</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F11" s="1">
-        <v>4</v>
-      </c>
-      <c r="G11" s="1">
-        <v>106</v>
-      </c>
-      <c r="H11" s="1">
-        <v>6</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C12" s="1">
-        <v>23007</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" s="1">
-        <v>4</v>
-      </c>
-      <c r="G12" s="1">
-        <v>106</v>
-      </c>
-      <c r="H12" s="1">
-        <v>7</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C13" s="1">
-        <v>23008</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F13" s="1">
-        <v>4</v>
-      </c>
-      <c r="G13" s="1">
-        <v>106</v>
-      </c>
-      <c r="H13" s="1">
-        <v>8</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C14" s="1">
-        <v>23009</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" s="1">
-        <v>4</v>
-      </c>
-      <c r="G14" s="1">
-        <v>106</v>
-      </c>
-      <c r="H14" s="1">
-        <v>9</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C15" s="1">
-        <v>23010</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="1">
-        <v>4</v>
-      </c>
-      <c r="G15" s="1">
-        <v>106</v>
-      </c>
-      <c r="H15" s="1">
-        <v>10</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C17" s="1">
-        <v>23101</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="1">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1">
-        <v>107</v>
-      </c>
-      <c r="H17" s="1">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C18" s="1">
-        <v>23102</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="1">
-        <v>4</v>
-      </c>
-      <c r="G18" s="1">
-        <v>107</v>
-      </c>
-      <c r="H18" s="1">
-        <v>2</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C19" s="1">
-        <v>23103</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="1">
-        <v>4</v>
-      </c>
-      <c r="G19" s="1">
-        <v>107</v>
-      </c>
-      <c r="H19" s="1">
-        <v>3</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C20" s="1">
-        <v>23104</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" s="1">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1">
-        <v>107</v>
-      </c>
-      <c r="H20" s="1">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C21" s="1">
-        <v>23105</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="1">
-        <v>4</v>
-      </c>
-      <c r="G21" s="1">
-        <v>107</v>
-      </c>
-      <c r="H21" s="1">
-        <v>1</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C22" s="1">
-        <v>23106</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" s="1">
-        <v>4</v>
-      </c>
-      <c r="G22" s="1">
-        <v>107</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C23" s="1">
-        <v>23107</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="1">
-        <v>4</v>
-      </c>
-      <c r="G23" s="1">
-        <v>107</v>
-      </c>
-      <c r="H23" s="1">
-        <v>1</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C24" s="1">
-        <v>23108</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="1">
-        <v>4</v>
-      </c>
-      <c r="G24" s="1">
-        <v>107</v>
-      </c>
-      <c r="H24" s="1">
-        <v>1</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C25" s="1">
-        <v>23109</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F25" s="1">
-        <v>4</v>
-      </c>
-      <c r="G25" s="1">
-        <v>107</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C26" s="1">
-        <v>23110</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="1">
-        <v>4</v>
-      </c>
-      <c r="G26" s="1">
-        <v>107</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C29" s="1">
-        <v>23201</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F29" s="1">
-        <v>4</v>
-      </c>
-      <c r="G29" s="1">
-        <v>108</v>
-      </c>
-      <c r="H29" s="1">
-        <v>1</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C30" s="1">
-        <v>23202</v>
-      </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F30" s="1">
-        <v>4</v>
-      </c>
-      <c r="G30" s="1">
-        <v>108</v>
-      </c>
-      <c r="H30" s="1">
-        <v>2</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C31" s="1">
-        <v>23203</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F31" s="1">
-        <v>4</v>
-      </c>
-      <c r="G31" s="1">
-        <v>108</v>
-      </c>
-      <c r="H31" s="1">
-        <v>3</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C32" s="1">
-        <v>23204</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F32" s="1">
-        <v>4</v>
-      </c>
-      <c r="G32" s="1">
-        <v>108</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="C33" s="1">
-        <v>23205</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F33" s="1">
-        <v>4</v>
-      </c>
-      <c r="G33" s="1">
-        <v>108</v>
-      </c>
-      <c r="H33" s="1">
-        <v>1</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="C34" s="1">
-        <v>23206</v>
-      </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F34" s="1">
-        <v>4</v>
-      </c>
-      <c r="G34" s="1">
-        <v>108</v>
-      </c>
-      <c r="H34" s="1">
-        <v>1</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:S27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="11.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="38.8333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1666666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="40.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="59.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="16" style="1" customWidth="1"/>
@@ -3145,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -3157,7 +2154,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -3204,7 +2201,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="59">
   <si>
     <t>#</t>
   </si>
@@ -144,7 +144,7 @@
     <t>8,8888,88</t>
   </si>
   <si>
-    <t>pl礼包</t>
+    <t>800w金币+8888铜矿+88黑铁矿</t>
   </si>
   <si>
     <t>qq500</t>
@@ -153,7 +153,7 @@
     <t>5,5555,55</t>
   </si>
   <si>
-    <t>入群礼包</t>
+    <t>500w金币+5555铜矿+55黑铁矿</t>
   </si>
   <si>
     <t>qq1000</t>
@@ -162,15 +162,15 @@
     <t>6,6666,66</t>
   </si>
   <si>
+    <t>600w金币+6666铜矿+66黑铁矿</t>
+  </si>
+  <si>
     <t>qq1500</t>
   </si>
   <si>
     <t>pf001</t>
   </si>
   <si>
-    <t>pf礼包</t>
-  </si>
-  <si>
     <t>pf002</t>
   </si>
   <si>
@@ -189,6 +189,9 @@
     <t>5,5000</t>
   </si>
   <si>
+    <t>500w金币+5000铜矿</t>
+  </si>
+  <si>
     <t>zc100</t>
   </si>
   <si>
@@ -196,6 +199,9 @@
   </si>
   <si>
     <t>5,100</t>
+  </si>
+  <si>
+    <t>500w金币+100黑铁矿</t>
   </si>
   <si>
     <t>dki309d!34</t>
@@ -1466,7 +1472,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:9">
@@ -1477,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>22</v>
@@ -1489,7 +1495,7 @@
         <v>24</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="1" customHeight="1" spans="1:9">
@@ -1502,7 +1508,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>22</v>
@@ -1514,7 +1520,7 @@
         <v>24</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:9">
@@ -1539,7 +1545,7 @@
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:9">
@@ -1577,6 +1583,9 @@
       <c r="H19" s="9" t="s">
         <v>39</v>
       </c>
+      <c r="I19" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
       <c r="C20" s="1">
@@ -1586,16 +1595,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>37</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
@@ -1843,19 +1855,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1866,19 +1878,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1889,19 +1901,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1912,19 +1924,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1935,19 +1947,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1958,19 +1970,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1991,7 +2003,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2142,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2154,7 +2166,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -2201,7 +2213,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -172,6 +172,15 @@
   </si>
   <si>
     <t>pf002</t>
+  </si>
+  <si>
+    <t>wujin888</t>
+  </si>
+  <si>
+    <t>18,18888,188</t>
+  </si>
+  <si>
+    <t>1800w金币+18888铜矿+188黑铁矿</t>
   </si>
   <si>
     <t>之后的及时删除</t>
@@ -1551,6 +1560,27 @@
     <row r="16" customFormat="1" customHeight="1" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
+      <c r="C16">
+        <v>12</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="17" customFormat="1" customHeight="1" spans="1:9">
       <c r="A17" s="1"/>
@@ -1561,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:9">
@@ -1572,19 +1602,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
@@ -1595,19 +1625,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
@@ -1855,19 +1885,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1878,19 +1908,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="H7" s="8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1901,19 +1931,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1924,19 +1954,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1947,19 +1977,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1970,19 +2000,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2003,7 +2033,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2154,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2166,7 +2196,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -2213,7 +2243,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="72">
   <si>
     <t>#</t>
   </si>
@@ -181,6 +181,36 @@
   </si>
   <si>
     <t>1800w金币+18888铜矿+188黑铁矿</t>
+  </si>
+  <si>
+    <t>cailiao666</t>
+  </si>
+  <si>
+    <t>5,5,5</t>
+  </si>
+  <si>
+    <t>40000001,40000002,40000003</t>
+  </si>
+  <si>
+    <t>25,5,1</t>
+  </si>
+  <si>
+    <t>25狼毛+5蛛丝+1雄狮利爪</t>
+  </si>
+  <si>
+    <t>shenbing666</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>5015,5016,5017,5018,5019</t>
+  </si>
+  <si>
+    <t>50,40,30,20,10</t>
+  </si>
+  <si>
+    <t>50神兵符1+40神兵符2+30神兵符3+20神兵符4+10神兵符5</t>
   </si>
   <si>
     <t>之后的及时删除</t>
@@ -936,6 +966,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1255,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1263,7 +1294,7 @@
     <col min="6" max="6" width="16.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="31.1666666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="25.8833333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="37.0166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="41.4166666666667" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1566,7 +1597,7 @@
       <c r="D16">
         <v>1</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F16" s="8" t="s">
@@ -1585,63 +1616,106 @@
     <row r="17" customFormat="1" customHeight="1" spans="1:9">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-    </row>
-    <row r="18" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A18" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="5" t="s">
+      <c r="C17">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
-      <c r="C19" s="1">
+      <c r="F17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="1">
+      <c r="I17" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18">
+        <v>14</v>
+      </c>
+      <c r="D18">
         <v>1</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="E18" s="3" t="s">
         <v>43</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" s="5" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A19" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:9">
       <c r="C20" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
-      <c r="H21" s="4"/>
+      <c r="C21" s="1">
+        <v>42</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="H22" s="4"/>
@@ -1650,15 +1724,15 @@
       <c r="H23" s="4"/>
     </row>
     <row r="24" customHeight="1" spans="1:9">
-      <c r="E24" s="6"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="6"/>
     </row>
     <row r="25" customHeight="1" spans="1:9">
+      <c r="E25" s="6"/>
       <c r="H25" s="4"/>
-    </row>
-    <row r="28" customHeight="1" spans="1:9">
-      <c r="H28" s="4"/>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" customHeight="1" spans="1:9">
+      <c r="H26" s="4"/>
     </row>
     <row r="29" customHeight="1" spans="1:9">
       <c r="H29" s="4"/>
@@ -1669,8 +1743,8 @@
     <row r="31" customHeight="1" spans="1:9">
       <c r="H31" s="4"/>
     </row>
-    <row r="33" customHeight="1" spans="8:11">
-      <c r="H33" s="4"/>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="H32" s="4"/>
     </row>
     <row r="34" customHeight="1" spans="8:11">
       <c r="H34" s="4"/>
@@ -1680,16 +1754,16 @@
     </row>
     <row r="36" customHeight="1" spans="8:11">
       <c r="H36" s="4"/>
-      <c r="K36" s="7"/>
     </row>
     <row r="37" customHeight="1" spans="8:11">
       <c r="H37" s="4"/>
+      <c r="K37" s="7"/>
     </row>
     <row r="38" customHeight="1" spans="8:11">
       <c r="H38" s="4"/>
     </row>
-    <row r="41" customHeight="1" spans="8:11">
-      <c r="H41" s="4"/>
+    <row r="39" customHeight="1" spans="8:11">
+      <c r="H39" s="4"/>
     </row>
     <row r="42" customHeight="1" spans="8:11">
       <c r="H42" s="4"/>
@@ -1697,8 +1771,8 @@
     <row r="43" customHeight="1" spans="8:11">
       <c r="H43" s="4"/>
     </row>
-    <row r="45" customHeight="1" spans="8:11">
-      <c r="H45" s="4"/>
+    <row r="44" customHeight="1" spans="8:11">
+      <c r="H44" s="4"/>
     </row>
     <row r="46" customHeight="1" spans="8:11">
       <c r="H46" s="4"/>
@@ -1709,8 +1783,8 @@
     <row r="48" customHeight="1" spans="8:11">
       <c r="H48" s="4"/>
     </row>
-    <row r="50" customHeight="1" spans="8:8">
-      <c r="H50" s="4"/>
+    <row r="49" customHeight="1" spans="8:8">
+      <c r="H49" s="4"/>
     </row>
     <row r="51" customHeight="1" spans="8:8">
       <c r="H51" s="4"/>
@@ -1718,8 +1792,8 @@
     <row r="52" customHeight="1" spans="8:8">
       <c r="H52" s="4"/>
     </row>
-    <row r="54" customHeight="1" spans="8:8">
-      <c r="H54" s="4"/>
+    <row r="53" customHeight="1" spans="8:8">
+      <c r="H53" s="4"/>
     </row>
     <row r="55" customHeight="1" spans="8:8">
       <c r="H55" s="4"/>
@@ -1733,11 +1807,14 @@
     <row r="58" customHeight="1" spans="8:8">
       <c r="H58" s="4"/>
     </row>
-    <row r="60" customHeight="1" spans="8:8">
-      <c r="H60" s="4"/>
-    </row>
-    <row r="62" customHeight="1" spans="8:8">
-      <c r="H62" s="4"/>
+    <row r="59" customHeight="1" spans="8:8">
+      <c r="H59" s="4"/>
+    </row>
+    <row r="61" customHeight="1" spans="8:8">
+      <c r="H61" s="4"/>
+    </row>
+    <row r="63" customHeight="1" spans="8:8">
+      <c r="H63" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1885,19 +1962,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1908,19 +1985,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1931,19 +2008,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1954,19 +2031,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1977,19 +2054,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2000,19 +2077,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2033,7 +2110,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2184,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2196,7 +2273,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -2243,7 +2320,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="75">
   <si>
     <t>#</t>
   </si>
@@ -211,6 +211,15 @@
   </si>
   <si>
     <t>50神兵符1+40神兵符2+30神兵符3+20神兵符4+10神兵符5</t>
+  </si>
+  <si>
+    <t>cailiao777</t>
+  </si>
+  <si>
+    <t>40000004,40000005,40000006</t>
+  </si>
+  <si>
+    <t>25虫卵+5蛇皮+1巨鳄之泪</t>
   </si>
   <si>
     <t>之后的及时删除</t>
@@ -1286,7 +1295,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1663,62 +1672,84 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A19" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="5" t="s">
+    <row r="19" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
-      <c r="C20" s="1">
+      <c r="F19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" s="8" t="s">
+      <c r="I19" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="8" t="s">
+    </row>
+    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A20" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:9">
       <c r="C21" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="I21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="1" t="s">
+    </row>
+    <row r="22" customHeight="1" spans="1:9">
+      <c r="C22" s="1">
+        <v>42</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:9">
-      <c r="H22" s="4"/>
+      <c r="F22" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="23" customHeight="1" spans="1:9">
       <c r="H23" s="4"/>
@@ -1727,15 +1758,15 @@
       <c r="H24" s="4"/>
     </row>
     <row r="25" customHeight="1" spans="1:9">
-      <c r="E25" s="6"/>
       <c r="H25" s="4"/>
-      <c r="I25" s="6"/>
     </row>
     <row r="26" customHeight="1" spans="1:9">
+      <c r="E26" s="6"/>
       <c r="H26" s="4"/>
-    </row>
-    <row r="29" customHeight="1" spans="1:9">
-      <c r="H29" s="4"/>
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" customHeight="1" spans="1:9">
+      <c r="H27" s="4"/>
     </row>
     <row r="30" customHeight="1" spans="1:9">
       <c r="H30" s="4"/>
@@ -1746,8 +1777,8 @@
     <row r="32" customHeight="1" spans="1:9">
       <c r="H32" s="4"/>
     </row>
-    <row r="34" customHeight="1" spans="8:11">
-      <c r="H34" s="4"/>
+    <row r="33" customHeight="1" spans="8:11">
+      <c r="H33" s="4"/>
     </row>
     <row r="35" customHeight="1" spans="8:11">
       <c r="H35" s="4"/>
@@ -1757,16 +1788,16 @@
     </row>
     <row r="37" customHeight="1" spans="8:11">
       <c r="H37" s="4"/>
-      <c r="K37" s="7"/>
     </row>
     <row r="38" customHeight="1" spans="8:11">
       <c r="H38" s="4"/>
+      <c r="K38" s="7"/>
     </row>
     <row r="39" customHeight="1" spans="8:11">
       <c r="H39" s="4"/>
     </row>
-    <row r="42" customHeight="1" spans="8:11">
-      <c r="H42" s="4"/>
+    <row r="40" customHeight="1" spans="8:11">
+      <c r="H40" s="4"/>
     </row>
     <row r="43" customHeight="1" spans="8:11">
       <c r="H43" s="4"/>
@@ -1774,8 +1805,8 @@
     <row r="44" customHeight="1" spans="8:11">
       <c r="H44" s="4"/>
     </row>
-    <row r="46" customHeight="1" spans="8:11">
-      <c r="H46" s="4"/>
+    <row r="45" customHeight="1" spans="8:11">
+      <c r="H45" s="4"/>
     </row>
     <row r="47" customHeight="1" spans="8:11">
       <c r="H47" s="4"/>
@@ -1786,8 +1817,8 @@
     <row r="49" customHeight="1" spans="8:8">
       <c r="H49" s="4"/>
     </row>
-    <row r="51" customHeight="1" spans="8:8">
-      <c r="H51" s="4"/>
+    <row r="50" customHeight="1" spans="8:8">
+      <c r="H50" s="4"/>
     </row>
     <row r="52" customHeight="1" spans="8:8">
       <c r="H52" s="4"/>
@@ -1795,8 +1826,8 @@
     <row r="53" customHeight="1" spans="8:8">
       <c r="H53" s="4"/>
     </row>
-    <row r="55" customHeight="1" spans="8:8">
-      <c r="H55" s="4"/>
+    <row r="54" customHeight="1" spans="8:8">
+      <c r="H54" s="4"/>
     </row>
     <row r="56" customHeight="1" spans="8:8">
       <c r="H56" s="4"/>
@@ -1810,11 +1841,14 @@
     <row r="59" customHeight="1" spans="8:8">
       <c r="H59" s="4"/>
     </row>
-    <row r="61" customHeight="1" spans="8:8">
-      <c r="H61" s="4"/>
-    </row>
-    <row r="63" customHeight="1" spans="8:8">
-      <c r="H63" s="4"/>
+    <row r="60" customHeight="1" spans="8:8">
+      <c r="H60" s="4"/>
+    </row>
+    <row r="62" customHeight="1" spans="8:8">
+      <c r="H62" s="4"/>
+    </row>
+    <row r="64" customHeight="1" spans="8:8">
+      <c r="H64" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1962,19 +1996,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -1985,19 +2019,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>60</v>
-      </c>
       <c r="H7" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2008,19 +2042,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2031,19 +2065,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2054,19 +2088,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2077,19 +2111,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2110,7 +2144,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2261,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2273,7 +2307,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
@@ -2320,7 +2354,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="更新码" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="79">
   <si>
     <t>#</t>
   </si>
@@ -292,6 +292,18 @@
   </si>
   <si>
     <t>大佬皮肤</t>
+  </si>
+  <si>
+    <t>sb1</t>
+  </si>
+  <si>
+    <t>100,80,60,40,20</t>
+  </si>
+  <si>
+    <t>sb2</t>
+  </si>
+  <si>
+    <t>200,160,120,80,40</t>
   </si>
 </sst>
 </file>
@@ -2178,7 +2190,7 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2213,12 +2225,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -2241,7 +2253,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -2264,7 +2276,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
@@ -2287,7 +2299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="3:19">
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
       <c r="C6" s="1">
         <v>40001</v>
       </c>
@@ -2310,7 +2322,55 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:19">
+    <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1">
+        <v>40002</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:19">
+      <c r="C8" s="1">
+        <v>40003</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="更新码" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="80">
   <si>
     <t>#</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t>25虫卵+5蛇皮+1巨鳄之泪</t>
+  </si>
+  <si>
+    <t>wujin777</t>
   </si>
   <si>
     <t>之后的及时删除</t>
@@ -1307,7 +1310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1709,62 +1712,84 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A20" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="5" t="s">
+    <row r="20" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
-      <c r="C21" s="1">
-        <v>41</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" s="5" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:9">
       <c r="C22" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22" s="8" t="s">
+    </row>
+    <row r="23" customHeight="1" spans="1:9">
+      <c r="C23" s="1">
+        <v>42</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="F23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="H23" s="9" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:9">
-      <c r="H23" s="4"/>
+      <c r="I23" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="24" customHeight="1" spans="1:9">
       <c r="H24" s="4"/>
@@ -1773,15 +1798,15 @@
       <c r="H25" s="4"/>
     </row>
     <row r="26" customHeight="1" spans="1:9">
-      <c r="E26" s="6"/>
       <c r="H26" s="4"/>
-      <c r="I26" s="6"/>
     </row>
     <row r="27" customHeight="1" spans="1:9">
+      <c r="E27" s="6"/>
       <c r="H27" s="4"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:9">
-      <c r="H30" s="4"/>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:9">
+      <c r="H28" s="4"/>
     </row>
     <row r="31" customHeight="1" spans="1:9">
       <c r="H31" s="4"/>
@@ -1792,8 +1817,8 @@
     <row r="33" customHeight="1" spans="8:11">
       <c r="H33" s="4"/>
     </row>
-    <row r="35" customHeight="1" spans="8:11">
-      <c r="H35" s="4"/>
+    <row r="34" customHeight="1" spans="8:11">
+      <c r="H34" s="4"/>
     </row>
     <row r="36" customHeight="1" spans="8:11">
       <c r="H36" s="4"/>
@@ -1803,16 +1828,16 @@
     </row>
     <row r="38" customHeight="1" spans="8:11">
       <c r="H38" s="4"/>
-      <c r="K38" s="7"/>
     </row>
     <row r="39" customHeight="1" spans="8:11">
       <c r="H39" s="4"/>
+      <c r="K39" s="7"/>
     </row>
     <row r="40" customHeight="1" spans="8:11">
       <c r="H40" s="4"/>
     </row>
-    <row r="43" customHeight="1" spans="8:11">
-      <c r="H43" s="4"/>
+    <row r="41" customHeight="1" spans="8:11">
+      <c r="H41" s="4"/>
     </row>
     <row r="44" customHeight="1" spans="8:11">
       <c r="H44" s="4"/>
@@ -1820,8 +1845,8 @@
     <row r="45" customHeight="1" spans="8:11">
       <c r="H45" s="4"/>
     </row>
-    <row r="47" customHeight="1" spans="8:11">
-      <c r="H47" s="4"/>
+    <row r="46" customHeight="1" spans="8:11">
+      <c r="H46" s="4"/>
     </row>
     <row r="48" customHeight="1" spans="8:11">
       <c r="H48" s="4"/>
@@ -1832,8 +1857,8 @@
     <row r="50" customHeight="1" spans="8:8">
       <c r="H50" s="4"/>
     </row>
-    <row r="52" customHeight="1" spans="8:8">
-      <c r="H52" s="4"/>
+    <row r="51" customHeight="1" spans="8:8">
+      <c r="H51" s="4"/>
     </row>
     <row r="53" customHeight="1" spans="8:8">
       <c r="H53" s="4"/>
@@ -1841,8 +1866,8 @@
     <row r="54" customHeight="1" spans="8:8">
       <c r="H54" s="4"/>
     </row>
-    <row r="56" customHeight="1" spans="8:8">
-      <c r="H56" s="4"/>
+    <row r="55" customHeight="1" spans="8:8">
+      <c r="H55" s="4"/>
     </row>
     <row r="57" customHeight="1" spans="8:8">
       <c r="H57" s="4"/>
@@ -1856,11 +1881,14 @@
     <row r="60" customHeight="1" spans="8:8">
       <c r="H60" s="4"/>
     </row>
-    <row r="62" customHeight="1" spans="8:8">
-      <c r="H62" s="4"/>
-    </row>
-    <row r="64" customHeight="1" spans="8:8">
-      <c r="H64" s="4"/>
+    <row r="61" customHeight="1" spans="8:8">
+      <c r="H61" s="4"/>
+    </row>
+    <row r="63" customHeight="1" spans="8:8">
+      <c r="H63" s="4"/>
+    </row>
+    <row r="65" customHeight="1" spans="8:8">
+      <c r="H65" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2008,19 +2036,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2031,19 +2059,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2054,19 +2082,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2077,19 +2105,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2100,19 +2128,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2123,19 +2151,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2156,7 +2184,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2307,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2319,7 +2347,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2332,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>44</v>
@@ -2341,7 +2369,7 @@
         <v>45</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>47</v>
@@ -2355,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>44</v>
@@ -2364,7 +2392,7 @@
         <v>45</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>47</v>
@@ -2414,7 +2442,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="84">
   <si>
     <t>#</t>
   </si>
@@ -168,6 +168,21 @@
     <t>qq1500</t>
   </si>
   <si>
+    <t>cailiao888</t>
+  </si>
+  <si>
+    <t>5,5,5</t>
+  </si>
+  <si>
+    <t>40000006,40000009,40000012</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>3巨鳄之泪+3尸王之心+3鹿血</t>
+  </si>
+  <si>
     <t>pf001</t>
   </si>
   <si>
@@ -184,9 +199,6 @@
   </si>
   <si>
     <t>cailiao666</t>
-  </si>
-  <si>
-    <t>5,5,5</t>
   </si>
   <si>
     <t>40000001,40000002,40000003</t>
@@ -1310,7 +1322,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1562,42 +1574,51 @@
         <v>25</v>
       </c>
     </row>
+    <row r="13" customHeight="1" spans="1:9">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="14" customFormat="1" customHeight="1" spans="1:9">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
-      <c r="C14" s="1">
-        <v>10</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:9">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>22</v>
@@ -1615,14 +1636,14 @@
     <row r="16" customFormat="1" customHeight="1" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16">
-        <v>12</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>35</v>
+      <c r="E16" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>22</v>
@@ -1631,34 +1652,34 @@
         <v>23</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="1" customHeight="1" spans="1:9">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="1" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1666,7 +1687,7 @@
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1675,144 +1696,172 @@
         <v>43</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="8" t="s">
         <v>49</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I19" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="1" customHeight="1" spans="1:9">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F20" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A21" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:9">
-      <c r="C22" s="1">
+      <c r="H21" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="1">
+      <c r="I21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" s="5" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A23" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:9">
+      <c r="C24" s="1">
+        <v>41</v>
+      </c>
+      <c r="D24" s="1">
         <v>1</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I22" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:9">
-      <c r="C23" s="1">
+      <c r="F24" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:9">
+      <c r="C25" s="1">
         <v>42</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D25" s="1">
         <v>1</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:9">
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:9">
-      <c r="H25" s="4"/>
+      <c r="G25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="26" customHeight="1" spans="1:9">
       <c r="H26" s="4"/>
     </row>
     <row r="27" customHeight="1" spans="1:9">
-      <c r="E27" s="6"/>
       <c r="H27" s="4"/>
-      <c r="I27" s="6"/>
     </row>
     <row r="28" customHeight="1" spans="1:9">
       <c r="H28" s="4"/>
     </row>
-    <row r="31" customHeight="1" spans="1:9">
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
-      <c r="H32" s="4"/>
+    <row r="29" customHeight="1" spans="1:9">
+      <c r="E29" s="6"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="6"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:9">
+      <c r="H30" s="4"/>
     </row>
     <row r="33" customHeight="1" spans="8:11">
       <c r="H33" s="4"/>
@@ -1820,61 +1869,61 @@
     <row r="34" customHeight="1" spans="8:11">
       <c r="H34" s="4"/>
     </row>
+    <row r="35" customHeight="1" spans="8:11">
+      <c r="H35" s="4"/>
+    </row>
     <row r="36" customHeight="1" spans="8:11">
       <c r="H36" s="4"/>
     </row>
-    <row r="37" customHeight="1" spans="8:11">
-      <c r="H37" s="4"/>
-    </row>
     <row r="38" customHeight="1" spans="8:11">
       <c r="H38" s="4"/>
     </row>
     <row r="39" customHeight="1" spans="8:11">
       <c r="H39" s="4"/>
-      <c r="K39" s="7"/>
     </row>
     <row r="40" customHeight="1" spans="8:11">
       <c r="H40" s="4"/>
     </row>
     <row r="41" customHeight="1" spans="8:11">
       <c r="H41" s="4"/>
-    </row>
-    <row r="44" customHeight="1" spans="8:11">
-      <c r="H44" s="4"/>
-    </row>
-    <row r="45" customHeight="1" spans="8:11">
-      <c r="H45" s="4"/>
+      <c r="K41" s="7"/>
+    </row>
+    <row r="42" customHeight="1" spans="8:11">
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" customHeight="1" spans="8:11">
+      <c r="H43" s="4"/>
     </row>
     <row r="46" customHeight="1" spans="8:11">
       <c r="H46" s="4"/>
     </row>
+    <row r="47" customHeight="1" spans="8:11">
+      <c r="H47" s="4"/>
+    </row>
     <row r="48" customHeight="1" spans="8:11">
       <c r="H48" s="4"/>
     </row>
-    <row r="49" customHeight="1" spans="8:8">
-      <c r="H49" s="4"/>
-    </row>
     <row r="50" customHeight="1" spans="8:8">
       <c r="H50" s="4"/>
     </row>
     <row r="51" customHeight="1" spans="8:8">
       <c r="H51" s="4"/>
     </row>
+    <row r="52" customHeight="1" spans="8:8">
+      <c r="H52" s="4"/>
+    </row>
     <row r="53" customHeight="1" spans="8:8">
       <c r="H53" s="4"/>
     </row>
-    <row r="54" customHeight="1" spans="8:8">
-      <c r="H54" s="4"/>
-    </row>
     <row r="55" customHeight="1" spans="8:8">
       <c r="H55" s="4"/>
     </row>
+    <row r="56" customHeight="1" spans="8:8">
+      <c r="H56" s="4"/>
+    </row>
     <row r="57" customHeight="1" spans="8:8">
       <c r="H57" s="4"/>
     </row>
-    <row r="58" customHeight="1" spans="8:8">
-      <c r="H58" s="4"/>
-    </row>
     <row r="59" customHeight="1" spans="8:8">
       <c r="H59" s="4"/>
     </row>
@@ -1884,11 +1933,17 @@
     <row r="61" customHeight="1" spans="8:8">
       <c r="H61" s="4"/>
     </row>
+    <row r="62" customHeight="1" spans="8:8">
+      <c r="H62" s="4"/>
+    </row>
     <row r="63" customHeight="1" spans="8:8">
       <c r="H63" s="4"/>
     </row>
     <row r="65" customHeight="1" spans="8:8">
       <c r="H65" s="4"/>
+    </row>
+    <row r="67" customHeight="1" spans="8:8">
+      <c r="H67" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2036,19 +2091,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2059,19 +2114,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="G7" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2082,19 +2137,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="H8" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2105,19 +2160,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2128,19 +2183,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2151,19 +2206,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2184,7 +2239,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2335,7 +2390,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2347,7 +2402,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2360,19 +2415,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:19">
@@ -2383,19 +2438,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2442,7 +2497,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="86">
   <si>
     <t>#</t>
   </si>
@@ -265,6 +265,12 @@
   </si>
   <si>
     <t>500w金币+100黑铁矿</t>
+  </si>
+  <si>
+    <t>bc102</t>
+  </si>
+  <si>
+    <t>666黑铁矿</t>
   </si>
   <si>
     <t>dki309d!34</t>
@@ -516,12 +522,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1847,7 +1853,27 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:9">
-      <c r="H26" s="4"/>
+      <c r="C26" s="1">
+        <v>43</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5002</v>
+      </c>
+      <c r="H26" s="4">
+        <v>666</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="27" customHeight="1" spans="1:9">
       <c r="H27" s="4"/>
@@ -2091,19 +2117,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2114,19 +2140,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2137,19 +2163,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2160,19 +2186,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2183,19 +2209,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2206,19 +2232,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2239,7 +2265,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2390,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2402,7 +2428,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2415,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>48</v>
@@ -2424,7 +2450,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>51</v>
@@ -2438,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>48</v>
@@ -2447,7 +2473,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>51</v>
@@ -2497,7 +2523,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="87">
   <si>
     <t>#</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>666黑铁矿</t>
+  </si>
+  <si>
+    <t>tt105</t>
   </si>
   <si>
     <t>dki309d!34</t>
@@ -1882,8 +1885,24 @@
       <c r="H28" s="4"/>
     </row>
     <row r="29" customHeight="1" spans="1:9">
-      <c r="E29" s="6"/>
-      <c r="H29" s="4"/>
+      <c r="C29" s="1">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="I29" s="6"/>
     </row>
     <row r="30" customHeight="1" spans="1:9">
@@ -2117,19 +2136,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2140,19 +2159,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2163,19 +2182,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2186,19 +2205,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2209,19 +2228,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2232,19 +2251,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2265,7 +2284,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2416,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2428,7 +2447,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2441,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>48</v>
@@ -2450,7 +2469,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>51</v>
@@ -2464,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>48</v>
@@ -2473,7 +2492,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>51</v>
@@ -2523,7 +2542,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="87">
   <si>
     <t>#</t>
   </si>
@@ -525,12 +525,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1885,6 +1885,12 @@
       <c r="H28" s="4"/>
     </row>
     <row r="29" customHeight="1" spans="1:9">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C29" s="1">
         <v>100</v>
       </c>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="88">
   <si>
     <t>#</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>wujin777</t>
+  </si>
+  <si>
+    <t>shenbing777</t>
   </si>
   <si>
     <t>之后的及时删除</t>
@@ -525,12 +528,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1795,18 +1798,34 @@
     <row r="22" customFormat="1" customHeight="1" spans="1:9">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="1"/>
+      <c r="C22">
+        <v>17</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="23" s="5" customFormat="1" customHeight="1" spans="1:9">
       <c r="A23" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:9">
@@ -1817,19 +1836,19 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
@@ -1840,19 +1859,19 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:9">
@@ -1863,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F26" s="1">
         <v>5</v>
@@ -1875,7 +1894,7 @@
         <v>666</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:9">
@@ -1898,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>34</v>
@@ -2142,19 +2161,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2165,19 +2184,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2188,19 +2207,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2211,19 +2230,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2234,19 +2253,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2257,19 +2276,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2290,7 +2309,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2441,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2453,7 +2472,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2466,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>48</v>
@@ -2475,7 +2494,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>51</v>
@@ -2489,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>48</v>
@@ -2498,7 +2517,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>51</v>
@@ -2548,7 +2567,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>#</t>
   </si>
@@ -237,7 +237,19 @@
     <t>wujin777</t>
   </si>
   <si>
-    <t>shenbing777</t>
+    <t>sxyz</t>
+  </si>
+  <si>
+    <t>cxyz</t>
+  </si>
+  <si>
+    <t>40000003,40000006,40000009,40000012</t>
+  </si>
+  <si>
+    <t>3,3,3,3</t>
+  </si>
+  <si>
+    <t>3雄狮利爪+3鳄鱼之类+3尸王之心+3鹿血</t>
   </si>
   <si>
     <t>之后的及时删除</t>
@@ -528,12 +540,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1334,7 +1346,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1820,49 +1832,51 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" s="5" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A23" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="5" t="s">
+    <row r="23" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23">
+        <v>18</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:9">
-      <c r="C24" s="1">
-        <v>41</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="F23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="H23" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="I23" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H24" s="9" t="s">
+    </row>
+    <row r="24" s="5" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A24" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="C25" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>64</v>
@@ -1876,7 +1890,7 @@
     </row>
     <row r="26" customHeight="1" spans="1:9">
       <c r="C26" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -1884,57 +1898,77 @@
       <c r="E26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:9">
+      <c r="C27" s="1">
+        <v>43</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="1">
         <v>5</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G27" s="1">
         <v>5002</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H27" s="4">
         <v>666</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:9">
-      <c r="H27" s="4"/>
+      <c r="I27" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="28" customHeight="1" spans="1:9">
       <c r="H28" s="4"/>
     </row>
     <row r="29" customHeight="1" spans="1:9">
-      <c r="A29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="1">
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:9">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1">
         <v>100</v>
       </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="8" t="s">
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G30" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="6"/>
-    </row>
-    <row r="30" customHeight="1" spans="1:9">
-      <c r="H30" s="4"/>
-    </row>
-    <row r="33" customHeight="1" spans="8:11">
-      <c r="H33" s="4"/>
+      <c r="I30" s="6"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="H31" s="4"/>
     </row>
     <row r="34" customHeight="1" spans="8:11">
       <c r="H34" s="4"/>
@@ -1945,8 +1979,8 @@
     <row r="36" customHeight="1" spans="8:11">
       <c r="H36" s="4"/>
     </row>
-    <row r="38" customHeight="1" spans="8:11">
-      <c r="H38" s="4"/>
+    <row r="37" customHeight="1" spans="8:11">
+      <c r="H37" s="4"/>
     </row>
     <row r="39" customHeight="1" spans="8:11">
       <c r="H39" s="4"/>
@@ -1956,16 +1990,16 @@
     </row>
     <row r="41" customHeight="1" spans="8:11">
       <c r="H41" s="4"/>
-      <c r="K41" s="7"/>
     </row>
     <row r="42" customHeight="1" spans="8:11">
       <c r="H42" s="4"/>
+      <c r="K42" s="7"/>
     </row>
     <row r="43" customHeight="1" spans="8:11">
       <c r="H43" s="4"/>
     </row>
-    <row r="46" customHeight="1" spans="8:11">
-      <c r="H46" s="4"/>
+    <row r="44" customHeight="1" spans="8:11">
+      <c r="H44" s="4"/>
     </row>
     <row r="47" customHeight="1" spans="8:11">
       <c r="H47" s="4"/>
@@ -1973,8 +2007,8 @@
     <row r="48" customHeight="1" spans="8:11">
       <c r="H48" s="4"/>
     </row>
-    <row r="50" customHeight="1" spans="8:8">
-      <c r="H50" s="4"/>
+    <row r="49" customHeight="1" spans="8:8">
+      <c r="H49" s="4"/>
     </row>
     <row r="51" customHeight="1" spans="8:8">
       <c r="H51" s="4"/>
@@ -1985,8 +2019,8 @@
     <row r="53" customHeight="1" spans="8:8">
       <c r="H53" s="4"/>
     </row>
-    <row r="55" customHeight="1" spans="8:8">
-      <c r="H55" s="4"/>
+    <row r="54" customHeight="1" spans="8:8">
+      <c r="H54" s="4"/>
     </row>
     <row r="56" customHeight="1" spans="8:8">
       <c r="H56" s="4"/>
@@ -1994,8 +2028,8 @@
     <row r="57" customHeight="1" spans="8:8">
       <c r="H57" s="4"/>
     </row>
-    <row r="59" customHeight="1" spans="8:8">
-      <c r="H59" s="4"/>
+    <row r="58" customHeight="1" spans="8:8">
+      <c r="H58" s="4"/>
     </row>
     <row r="60" customHeight="1" spans="8:8">
       <c r="H60" s="4"/>
@@ -2009,11 +2043,14 @@
     <row r="63" customHeight="1" spans="8:8">
       <c r="H63" s="4"/>
     </row>
-    <row r="65" customHeight="1" spans="8:8">
-      <c r="H65" s="4"/>
-    </row>
-    <row r="67" customHeight="1" spans="8:8">
-      <c r="H67" s="4"/>
+    <row r="64" customHeight="1" spans="8:8">
+      <c r="H64" s="4"/>
+    </row>
+    <row r="66" customHeight="1" spans="8:8">
+      <c r="H66" s="4"/>
+    </row>
+    <row r="68" customHeight="1" spans="8:8">
+      <c r="H68" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2161,19 +2198,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2184,19 +2221,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="G7" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2207,19 +2244,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="H8" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2230,19 +2267,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2253,19 +2290,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2276,19 +2313,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2309,7 +2346,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2460,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2472,7 +2509,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2485,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>48</v>
@@ -2494,7 +2531,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>51</v>
@@ -2508,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>48</v>
@@ -2517,7 +2554,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>51</v>
@@ -2567,7 +2604,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="93">
   <si>
     <t>#</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>666黑铁矿</t>
+  </si>
+  <si>
+    <t>bc106</t>
   </si>
   <si>
     <t>tt105</t>
@@ -1935,7 +1938,27 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:9">
-      <c r="H28" s="4"/>
+      <c r="C28" s="1">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="1">
+        <v>5</v>
+      </c>
+      <c r="G28" s="1">
+        <v>5002</v>
+      </c>
+      <c r="H28" s="4">
+        <v>666</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="29" customHeight="1" spans="1:9">
       <c r="H29" s="4"/>
@@ -1954,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>34</v>
@@ -2198,19 +2221,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2221,19 +2244,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2244,19 +2267,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2267,19 +2290,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2290,19 +2313,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2313,19 +2336,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2346,7 +2369,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2497,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2509,7 +2532,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2522,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>48</v>
@@ -2531,7 +2554,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>51</v>
@@ -2545,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>48</v>
@@ -2554,7 +2577,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>51</v>
@@ -2604,7 +2627,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="更新码" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="94">
   <si>
     <t>#</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>bc106</t>
+  </si>
+  <si>
+    <t>gx109</t>
   </si>
   <si>
     <t>tt105</t>
@@ -1349,7 +1352,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1961,40 +1964,60 @@
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:9">
-      <c r="H29" s="4"/>
+      <c r="C29" s="1">
+        <v>45</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5</v>
+      </c>
+      <c r="G29" s="1">
+        <v>5002</v>
+      </c>
+      <c r="H29" s="4">
+        <v>1666</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="30" customHeight="1" spans="1:9">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1">
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1">
         <v>100</v>
       </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F30" s="8" t="s">
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G31" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H31" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I30" s="6"/>
-    </row>
-    <row r="31" customHeight="1" spans="1:9">
-      <c r="H31" s="4"/>
-    </row>
-    <row r="34" customHeight="1" spans="8:11">
-      <c r="H34" s="4"/>
+      <c r="I31" s="6"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="H32" s="4"/>
     </row>
     <row r="35" customHeight="1" spans="8:11">
       <c r="H35" s="4"/>
@@ -2005,8 +2028,8 @@
     <row r="37" customHeight="1" spans="8:11">
       <c r="H37" s="4"/>
     </row>
-    <row r="39" customHeight="1" spans="8:11">
-      <c r="H39" s="4"/>
+    <row r="38" customHeight="1" spans="8:11">
+      <c r="H38" s="4"/>
     </row>
     <row r="40" customHeight="1" spans="8:11">
       <c r="H40" s="4"/>
@@ -2016,16 +2039,16 @@
     </row>
     <row r="42" customHeight="1" spans="8:11">
       <c r="H42" s="4"/>
-      <c r="K42" s="7"/>
     </row>
     <row r="43" customHeight="1" spans="8:11">
       <c r="H43" s="4"/>
+      <c r="K43" s="7"/>
     </row>
     <row r="44" customHeight="1" spans="8:11">
       <c r="H44" s="4"/>
     </row>
-    <row r="47" customHeight="1" spans="8:11">
-      <c r="H47" s="4"/>
+    <row r="45" customHeight="1" spans="8:11">
+      <c r="H45" s="4"/>
     </row>
     <row r="48" customHeight="1" spans="8:11">
       <c r="H48" s="4"/>
@@ -2033,8 +2056,8 @@
     <row r="49" customHeight="1" spans="8:8">
       <c r="H49" s="4"/>
     </row>
-    <row r="51" customHeight="1" spans="8:8">
-      <c r="H51" s="4"/>
+    <row r="50" customHeight="1" spans="8:8">
+      <c r="H50" s="4"/>
     </row>
     <row r="52" customHeight="1" spans="8:8">
       <c r="H52" s="4"/>
@@ -2045,8 +2068,8 @@
     <row r="54" customHeight="1" spans="8:8">
       <c r="H54" s="4"/>
     </row>
-    <row r="56" customHeight="1" spans="8:8">
-      <c r="H56" s="4"/>
+    <row r="55" customHeight="1" spans="8:8">
+      <c r="H55" s="4"/>
     </row>
     <row r="57" customHeight="1" spans="8:8">
       <c r="H57" s="4"/>
@@ -2054,8 +2077,8 @@
     <row r="58" customHeight="1" spans="8:8">
       <c r="H58" s="4"/>
     </row>
-    <row r="60" customHeight="1" spans="8:8">
-      <c r="H60" s="4"/>
+    <row r="59" customHeight="1" spans="8:8">
+      <c r="H59" s="4"/>
     </row>
     <row r="61" customHeight="1" spans="8:8">
       <c r="H61" s="4"/>
@@ -2069,11 +2092,14 @@
     <row r="64" customHeight="1" spans="8:8">
       <c r="H64" s="4"/>
     </row>
-    <row r="66" customHeight="1" spans="8:8">
-      <c r="H66" s="4"/>
-    </row>
-    <row r="68" customHeight="1" spans="8:8">
-      <c r="H68" s="4"/>
+    <row r="65" customHeight="1" spans="8:8">
+      <c r="H65" s="4"/>
+    </row>
+    <row r="67" customHeight="1" spans="8:8">
+      <c r="H67" s="4"/>
+    </row>
+    <row r="69" customHeight="1" spans="8:8">
+      <c r="H69" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2221,19 +2247,19 @@
         <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2244,19 +2270,19 @@
         <v>99</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2267,19 +2293,19 @@
         <v>99</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2290,19 +2316,19 @@
         <v>99</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2313,19 +2339,19 @@
         <v>99</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2336,19 +2362,19 @@
         <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:19">
@@ -2369,7 +2395,7 @@
     </row>
     <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" s="4"/>
     </row>
@@ -2520,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -2532,7 +2558,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="18" customHeight="1" spans="1:19">
@@ -2545,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>48</v>
@@ -2554,7 +2580,7 @@
         <v>49</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>51</v>
@@ -2568,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>48</v>
@@ -2577,7 +2603,7 @@
         <v>49</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>51</v>
@@ -2627,7 +2653,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="G26" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" s="4"/>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="更新码" sheetId="1" r:id="rId1"/>
@@ -546,12 +546,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1017,7 +1017,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1026,13 +1026,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1352,14 +1358,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
     <col min="5" max="5" width="15.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="31.1666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.8833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.8833333333333" style="6" customWidth="1"/>
     <col min="9" max="9" width="41.4166666666667" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
@@ -1390,7 +1396,7 @@
       <c r="G3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -1413,7 +1419,7 @@
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -1436,7 +1442,7 @@
       <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -1453,13 +1459,13 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="11" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3">
         <v>10001</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="12" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1476,13 +1482,13 @@
       <c r="E7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="11" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="3">
         <v>10002</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="12" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1499,13 +1505,13 @@
       <c r="E8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="11" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="3">
         <v>10003</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="12" t="s">
         <v>15</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1522,13 +1528,13 @@
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1545,13 +1551,13 @@
       <c r="E10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="12" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1568,13 +1574,13 @@
       <c r="E11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1591,13 +1597,13 @@
       <c r="E12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1614,13 +1620,13 @@
       <c r="E13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="12" t="s">
         <v>36</v>
       </c>
       <c r="I13" s="3" t="s">
@@ -1635,7 +1641,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="1"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="1"/>
+      <c r="H14" s="6"/>
       <c r="I14" s="3"/>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:9">
@@ -1650,13 +1656,13 @@
       <c r="E15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -1675,13 +1681,13 @@
       <c r="E16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1700,13 +1706,13 @@
       <c r="E17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -1725,13 +1731,13 @@
       <c r="E18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="12" t="s">
         <v>45</v>
       </c>
       <c r="I18" s="3" t="s">
@@ -1750,16 +1756,16 @@
       <c r="E19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="13" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1775,13 +1781,13 @@
       <c r="E20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="12" t="s">
         <v>45</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -1800,13 +1806,13 @@
       <c r="E21" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="12" t="s">
         <v>41</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -1825,16 +1831,16 @@
       <c r="E22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="13" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1850,13 +1856,13 @@
       <c r="E23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="12" t="s">
         <v>59</v>
       </c>
       <c r="I23" s="3" t="s">
@@ -1870,6 +1876,7 @@
       <c r="B24" s="5" t="s">
         <v>61</v>
       </c>
+      <c r="H24" s="8"/>
     </row>
     <row r="25" customHeight="1" spans="1:9">
       <c r="C25" s="1">
@@ -1881,13 +1888,13 @@
       <c r="E25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="12" t="s">
         <v>65</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -1904,13 +1911,13 @@
       <c r="E26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="12" t="s">
         <v>69</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -1933,7 +1940,7 @@
       <c r="G27" s="1">
         <v>5002</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="6">
         <v>666</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -1956,7 +1963,7 @@
       <c r="G28" s="1">
         <v>5002</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="6">
         <v>666</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -1979,16 +1986,13 @@
       <c r="G29" s="1">
         <v>5002</v>
       </c>
-      <c r="H29" s="4">
-        <v>1666</v>
+      <c r="H29" s="6">
+        <v>2666</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:9">
-      <c r="H30" s="4"/>
-    </row>
     <row r="31" customHeight="1" spans="1:9">
       <c r="A31" s="1" t="s">
         <v>0</v>
@@ -2002,104 +2006,22 @@
       <c r="D31" s="1">
         <v>1</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
-      <c r="H32" s="4"/>
-    </row>
-    <row r="35" customHeight="1" spans="8:11">
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" customHeight="1" spans="8:11">
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" customHeight="1" spans="8:11">
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" customHeight="1" spans="8:11">
-      <c r="H38" s="4"/>
-    </row>
-    <row r="40" customHeight="1" spans="8:11">
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" customHeight="1" spans="8:11">
-      <c r="H41" s="4"/>
-    </row>
-    <row r="42" customHeight="1" spans="8:11">
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" customHeight="1" spans="8:11">
-      <c r="H43" s="4"/>
-      <c r="K43" s="7"/>
-    </row>
-    <row r="44" customHeight="1" spans="8:11">
-      <c r="H44" s="4"/>
-    </row>
-    <row r="45" customHeight="1" spans="8:11">
-      <c r="H45" s="4"/>
-    </row>
-    <row r="48" customHeight="1" spans="8:11">
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" customHeight="1" spans="8:8">
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" customHeight="1" spans="8:8">
-      <c r="H50" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="8:8">
-      <c r="H52" s="4"/>
-    </row>
-    <row r="53" customHeight="1" spans="8:8">
-      <c r="H53" s="4"/>
-    </row>
-    <row r="54" customHeight="1" spans="8:8">
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" customHeight="1" spans="8:8">
-      <c r="H55" s="4"/>
-    </row>
-    <row r="57" customHeight="1" spans="8:8">
-      <c r="H57" s="4"/>
-    </row>
-    <row r="58" customHeight="1" spans="8:8">
-      <c r="H58" s="4"/>
-    </row>
-    <row r="59" customHeight="1" spans="8:8">
-      <c r="H59" s="4"/>
-    </row>
-    <row r="61" customHeight="1" spans="8:8">
-      <c r="H61" s="4"/>
-    </row>
-    <row r="62" customHeight="1" spans="8:8">
-      <c r="H62" s="4"/>
-    </row>
-    <row r="63" customHeight="1" spans="8:8">
-      <c r="H63" s="4"/>
-    </row>
-    <row r="64" customHeight="1" spans="8:8">
-      <c r="H64" s="4"/>
-    </row>
-    <row r="65" customHeight="1" spans="8:8">
-      <c r="H65" s="4"/>
-    </row>
-    <row r="67" customHeight="1" spans="8:8">
-      <c r="H67" s="4"/>
-    </row>
-    <row r="69" customHeight="1" spans="8:8">
-      <c r="H69" s="4"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="43" customHeight="1" spans="11:11">
+      <c r="K43" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2249,13 +2171,13 @@
       <c r="E6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="11" t="s">
         <v>79</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -2272,13 +2194,13 @@
       <c r="E7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="11" t="s">
         <v>79</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -2295,13 +2217,13 @@
       <c r="E8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="11" t="s">
         <v>79</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -2318,13 +2240,13 @@
       <c r="E9" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="11" t="s">
         <v>84</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -2341,13 +2263,13 @@
       <c r="E10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -2364,13 +2286,13 @@
       <c r="E11" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="11" t="s">
         <v>79</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -2548,13 +2470,13 @@
       <c r="E6" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="11" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3">
         <v>10004</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="14" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -2573,16 +2495,16 @@
       <c r="E7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="13" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2596,16 +2518,16 @@
       <c r="E8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="13" t="s">
         <v>51</v>
       </c>
     </row>

--- a/Excel/CodeConfig.xlsx
+++ b/Excel/CodeConfig.xlsx
@@ -291,7 +291,7 @@
     <t>bc106</t>
   </si>
   <si>
-    <t>gx109</t>
+    <t>gx110</t>
   </si>
   <si>
     <t>tt105</t>
@@ -546,12 +546,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
